--- a/figs/data/fig7_mixV_v4.xlsx
+++ b/figs/data/fig7_mixV_v4.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림7 v4 학습" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판단별 원자료" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림(이미지)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림7 v4 학습" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판단별 원자료" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,6 +535,36 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10252710" cy="4774882"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>16</col>
       <colOff>0</colOff>
       <row>1</row>
@@ -846,6 +877,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5179,7 +5224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/figs/data/fig7_mixV_v4.xlsx
+++ b/figs/data/fig7_mixV_v4.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림(이미지)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림7 v4 학습" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판단별 원자료" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="그림7 v4 학습" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판단별 원자료" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -311,135 +310,6 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'그림7 v4 학습'!K1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'그림7 v4 학습'!$J$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'그림7 v4 학습'!$K$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'그림7 v4 학습'!M1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'그림7 v4 학습'!$L$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'그림7 v4 학습'!$M$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'그림7 v4 학습'!O1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'그림7 v4 학습'!$N$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'그림7 v4 학습'!$O$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -504,26 +374,6 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
-      <legendEntry>
-        <idx val="2"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="3"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="4"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="5"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="6"/>
-        <delete val="1"/>
-      </legendEntry>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -535,37 +385,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10252710" cy="4774882"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>16</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -877,21 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:X433"/>
+  <dimension ref="A1:R433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,52 +723,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>선1 x</t>
+          <t>→ 2회차 4 5 6 7번 구간 x</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>선1</t>
+          <t>→ 2회차 4 5 6 7번 구간</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>선2 x</t>
+          <t>→ 3회차 8 9번 구간 x</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>선2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>라벨1 x</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>1회차 1 2 3번 구간</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>라벨2 x</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>2회차 4 5 6 7번 구간</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>라벨3 x</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>3회차 8 9번 구간</t>
+          <t>→ 3회차 8 9번 구간</t>
         </is>
       </c>
     </row>
@@ -991,24 +767,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>48</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>48</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1441,42 +1199,42 @@
       <c r="D32" t="n">
         <v>12</v>
       </c>
-      <c r="Q32" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>걸친 구간</t>
         </is>
       </c>
-      <c r="S32" s="1" t="inlineStr">
+      <c r="M32" s="1" t="inlineStr">
         <is>
           <t>시작(h)</t>
         </is>
       </c>
-      <c r="T32" s="1" t="inlineStr">
+      <c r="N32" s="1" t="inlineStr">
         <is>
           <t>끝(h)</t>
         </is>
       </c>
-      <c r="U32" s="1" t="inlineStr">
+      <c r="O32" s="1" t="inlineStr">
         <is>
           <t>시험 횟수</t>
         </is>
       </c>
-      <c r="V32" s="1" t="inlineStr">
+      <c r="P32" s="1" t="inlineStr">
         <is>
           <t>처음 후보</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
+      <c r="Q32" s="1" t="inlineStr">
         <is>
           <t>최소 후보</t>
         </is>
       </c>
-      <c r="X32" s="1" t="inlineStr">
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>마지막 최고 후보</t>
         </is>
@@ -1495,30 +1253,30 @@
       <c r="D33" t="n">
         <v>11</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>1.YCSB-A, 2.OLTP, 3.Varmail</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="n">
+      <c r="N33" t="n">
         <v>3.59</v>
       </c>
-      <c r="U33" t="n">
+      <c r="O33" t="n">
         <v>1224</v>
       </c>
-      <c r="V33" t="n">
+      <c r="P33" t="n">
         <v>45</v>
       </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1535,30 +1293,30 @@
       <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>4.YCSB-A, 5.YCSB-B, 6.FIO-Fast, 7.Varmail</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="M34" t="n">
         <v>3.61</v>
       </c>
-      <c r="T34" t="n">
+      <c r="N34" t="n">
         <v>7.94</v>
       </c>
-      <c r="U34" t="n">
+      <c r="O34" t="n">
         <v>255</v>
       </c>
-      <c r="V34" t="n">
+      <c r="P34" t="n">
         <v>11</v>
       </c>
-      <c r="W34" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" t="n">
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
         <v>37</v>
       </c>
     </row>
@@ -1575,30 +1333,30 @@
       <c r="D35" t="n">
         <v>9</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>8.YCSB-A, 9.OLTP</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="M35" t="n">
         <v>7.96</v>
       </c>
-      <c r="T35" t="n">
+      <c r="N35" t="n">
         <v>10.07</v>
       </c>
-      <c r="U35" t="n">
+      <c r="O35" t="n">
         <v>226</v>
       </c>
-      <c r="V35" t="n">
+      <c r="P35" t="n">
         <v>7</v>
       </c>
-      <c r="W35" t="n">
-        <v>6</v>
-      </c>
-      <c r="X35" t="n">
+      <c r="Q35" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5224,7 +4982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/figs/data/fig7_mixV_v4.xlsx
+++ b/figs/data/fig7_mixV_v4.xlsx
@@ -205,9 +205,6 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
               <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
